--- a/data/trans_orig/P36BPD11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023</t>
+          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243682</t>
+          <t>244851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>288637</t>
+          <t>289947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262085</t>
+          <t>260570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>298339</t>
+          <t>296447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>517434</t>
+          <t>518703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577231</t>
+          <t>574461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163172</t>
+          <t>160193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205711</t>
+          <t>204495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108298</t>
+          <t>108535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141425</t>
+          <t>142361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277947</t>
+          <t>281487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>333980</t>
+          <t>336061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>33758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>54707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81650</t>
+          <t>82906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116496</t>
+          <t>114848</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202522</t>
+          <t>202436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247588</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183920</t>
+          <t>182979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217359</t>
+          <t>216857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397337</t>
+          <t>397289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455221</t>
+          <t>454850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142393</t>
+          <t>142070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183937</t>
+          <t>185794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113123</t>
+          <t>112689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>143872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,47 +1349,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>37,68%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>290941</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>263944</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>316832</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>37,99%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>290941</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>264433</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>317716</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>31,7%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51568</t>
+          <t>51739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84749</t>
+          <t>84360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41839</t>
+          <t>42423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65660</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99485</t>
+          <t>102204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139874</t>
+          <t>140274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277846</t>
+          <t>275315</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>579722</t>
+          <t>573842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73520</t>
+          <t>74929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94418</t>
+          <t>94704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>367028</t>
+          <t>370643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>703437</t>
+          <t>681657</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60974</t>
+          <t>63415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273460</t>
+          <t>271662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49939</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>107898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329985</t>
+          <t>323977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124300</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145145</t>
+          <t>145306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>441611</t>
+          <t>446445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>514552</t>
+          <t>518205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>452205</t>
+          <t>453496</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>759533</t>
+          <t>769270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>923850</t>
+          <t>928826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1346473</t>
+          <t>1370214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326386</t>
+          <t>327948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393941</t>
+          <t>395435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149040</t>
+          <t>144955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365487</t>
+          <t>366538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433874</t>
+          <t>436933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728783</t>
+          <t>729472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171953</t>
+          <t>170114</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227033</t>
+          <t>222561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165597</t>
+          <t>166906</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216811</t>
+          <t>206135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>372241</t>
+          <t>369115</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165597</t>
+          <t>166263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209236</t>
+          <t>208401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239875</t>
+          <t>245982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375449</t>
+          <t>375718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426992</t>
+          <t>418877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>567624</t>
+          <t>565360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162325</t>
+          <t>163882</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>208852</t>
+          <t>209747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>305069</t>
+          <t>302564</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>488190</t>
+          <t>467652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>485119</t>
+          <t>485693</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>672351</t>
+          <t>670620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84046</t>
+          <t>84548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123076</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105736</t>
+          <t>111125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231362</t>
+          <t>243888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205000</t>
+          <t>205961</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335685</t>
+          <t>343249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106595</t>
+          <t>104306</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306996</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>360335</t>
+          <t>360149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>377701</t>
+          <t>375858</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>446914</t>
+          <t>446219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84280</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135748</t>
+          <t>135555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>276416</t>
+          <t>277487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>328505</t>
+          <t>329586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>377480</t>
+          <t>374542</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>447565</t>
+          <t>450109</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83561</t>
+          <t>80611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105177</t>
+          <t>105246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147404</t>
+          <t>146436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147825</t>
+          <t>146134</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>212078</t>
+          <t>213341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1511042</t>
+          <t>1508907</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2067513</t>
+          <t>2121677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1650193</t>
+          <t>1647803</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2103222</t>
+          <t>2109768</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3217889</t>
+          <t>3224444</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3997338</t>
+          <t>3936661</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>890224</t>
+          <t>867165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1276416</t>
+          <t>1271774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1052071</t>
+          <t>1058090</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1391178</t>
+          <t>1393704</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2082364</t>
+          <t>2113025</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2634668</t>
+          <t>2615961</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>419336</t>
+          <t>405736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>609045</t>
+          <t>610143</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>434426</t>
+          <t>441126</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>605320</t>
+          <t>606681</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>910191</t>
+          <t>927805</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1177833</t>
+          <t>1178559</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>266449</t>
+          <t>288451</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>244851</t>
+          <t>264668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289947</t>
+          <t>312763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>280162</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>260570</t>
+          <t>291042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296447</t>
+          <t>327698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>546611</t>
+          <t>596833</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>518703</t>
+          <t>565505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574461</t>
+          <t>625456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>182906</t>
+          <t>198964</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160193</t>
+          <t>177450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204495</t>
+          <t>221671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124618</t>
+          <t>132411</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108535</t>
+          <t>114745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142361</t>
+          <t>149633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>307524</t>
+          <t>331375</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281487</t>
+          <t>303313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>336061</t>
+          <t>361115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55858</t>
+          <t>63204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70281</t>
+          <t>78988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42687</t>
+          <t>47617</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54707</t>
+          <t>59978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>98545</t>
+          <t>110821</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82906</t>
+          <t>93217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114848</t>
+          <t>131236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224199</t>
+          <t>236584</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202436</t>
+          <t>212707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>258731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>200407</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182979</t>
+          <t>203064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216857</t>
+          <t>238649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>424605</t>
+          <t>457496</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397289</t>
+          <t>425409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454850</t>
+          <t>485022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>175079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142070</t>
+          <t>153768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>185794</t>
+          <t>195680</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127830</t>
+          <t>141164</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112689</t>
+          <t>125076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143872</t>
+          <t>158991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>290941</t>
+          <t>316243</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>263944</t>
+          <t>289397</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>316832</t>
+          <t>345929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51739</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84360</t>
+          <t>89935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>60329</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66589</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118526</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102204</t>
+          <t>113612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140274</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381861</t>
+          <t>422405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834073</t>
+          <t>905617</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834073</t>
+          <t>905617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834073</t>
+          <t>905617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>427055</t>
+          <t>209206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275315</t>
+          <t>184062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>573842</t>
+          <t>230898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84208</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74929</t>
+          <t>86149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94704</t>
+          <t>109034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>511263</t>
+          <t>305779</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370643</t>
+          <t>281038</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>681657</t>
+          <t>329661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>165716</t>
+          <t>180703</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63415</t>
+          <t>158244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271662</t>
+          <t>201763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60148</t>
+          <t>66310</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>77192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>225864</t>
+          <t>247013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107898</t>
+          <t>223081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>323977</t>
+          <t>271143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75494</t>
+          <t>81703</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>65683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129843</t>
+          <t>100143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>24614</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>98048</t>
+          <t>106317</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145306</t>
+          <t>126454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>480829</t>
+          <t>516815</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>446445</t>
+          <t>480961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>518205</t>
+          <t>551037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>570101</t>
+          <t>407049</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>453496</t>
+          <t>381240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>769270</t>
+          <t>430664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1050930</t>
+          <t>923864</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>928826</t>
+          <t>878779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1370214</t>
+          <t>967206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>359648</t>
+          <t>392791</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327948</t>
+          <t>360458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395435</t>
+          <t>429351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>282200</t>
+          <t>309818</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144955</t>
+          <t>286384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366538</t>
+          <t>336069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>641847</t>
+          <t>702609</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>436933</t>
+          <t>661732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729472</t>
+          <t>748906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>194343</t>
+          <t>222237</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170114</t>
+          <t>193047</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222561</t>
+          <t>251962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>125064</t>
+          <t>143550</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>124227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166906</t>
+          <t>164547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>319407</t>
+          <t>365787</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>206135</t>
+          <t>332696</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>403531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>860417</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>860417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>860417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012184</t>
+          <t>1992260</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012184</t>
+          <t>1992260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012184</t>
+          <t>1992260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>186611</t>
+          <t>243501</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166263</t>
+          <t>218096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208401</t>
+          <t>269422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>328707</t>
+          <t>362509</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245982</t>
+          <t>339259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>387320</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>515318</t>
+          <t>606009</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418877</t>
+          <t>573394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>565360</t>
+          <t>642096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>184402</t>
+          <t>203795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163882</t>
+          <t>179445</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>209747</t>
+          <t>231000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>360671</t>
+          <t>331427</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>302564</t>
+          <t>308591</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>467652</t>
+          <t>356459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>545073</t>
+          <t>535222</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>485693</t>
+          <t>499730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>670620</t>
+          <t>569523</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>102137</t>
+          <t>117184</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84548</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124708</t>
+          <t>139522</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>149687</t>
+          <t>134456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111125</t>
+          <t>114878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243888</t>
+          <t>153715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>251824</t>
+          <t>251641</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205961</t>
+          <t>225188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343249</t>
+          <t>281380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473150</t>
+          <t>564481</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473150</t>
+          <t>564481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473150</t>
+          <t>564481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>839065</t>
+          <t>828392</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839065</t>
+          <t>828392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>839065</t>
+          <t>828392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1312216</t>
+          <t>1392872</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312216</t>
+          <t>1392872</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312216</t>
+          <t>1392872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79762</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>59120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104306</t>
+          <t>104011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>333174</t>
+          <t>367859</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307019</t>
+          <t>341515</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>360149</t>
+          <t>394304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>412937</t>
+          <t>446757</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>375858</t>
+          <t>411706</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>446219</t>
+          <t>481808</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>109195</t>
+          <t>110360</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>88313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135555</t>
+          <t>133267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>302883</t>
+          <t>333973</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>277487</t>
+          <t>305184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329586</t>
+          <t>360533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>412079</t>
+          <t>444332</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374542</t>
+          <t>406819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>450109</t>
+          <t>479403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80611</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>124285</t>
+          <t>141405</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105246</t>
+          <t>121747</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146436</t>
+          <t>165088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>175834</t>
+          <t>189375</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146134</t>
+          <t>161055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213341</t>
+          <t>223059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760342</t>
+          <t>843237</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760342</t>
+          <t>843237</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760342</t>
+          <t>843237</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000850</t>
+          <t>1080464</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000850</t>
+          <t>1080464</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000850</t>
+          <t>1080464</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1664904</t>
+          <t>1573454</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1508907</t>
+          <t>1510044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2121677</t>
+          <t>1635411</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1796760</t>
+          <t>1763284</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1647803</t>
+          <t>1708757</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2109768</t>
+          <t>1814473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3461663</t>
+          <t>3336738</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3224444</t>
+          <t>3253050</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3936661</t>
+          <t>3419076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1164977</t>
+          <t>1261692</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>867165</t>
+          <t>1199662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1271774</t>
+          <t>1324319</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1258351</t>
+          <t>1315102</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1058090</t>
+          <t>1266007</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1393704</t>
+          <t>1366871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2423328</t>
+          <t>2576794</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2113025</t>
+          <t>2495067</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2615961</t>
+          <t>2658647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>544284</t>
+          <t>603847</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>405736</t>
+          <t>553380</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>610143</t>
+          <t>655405</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>517901</t>
+          <t>551972</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>441126</t>
+          <t>510482</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>606681</t>
+          <t>591085</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1062185</t>
+          <t>1155819</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>927805</t>
+          <t>1095894</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1178559</t>
+          <t>1221478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374165</t>
+          <t>3438993</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374165</t>
+          <t>3438993</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374165</t>
+          <t>3438993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3573011</t>
+          <t>3630358</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3573011</t>
+          <t>3630358</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3573011</t>
+          <t>3630358</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6947176</t>
+          <t>7069351</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6947176</t>
+          <t>7069351</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6947176</t>
+          <t>7069351</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
